--- a/public/examples/golomt-bank-statement-sample.xlsx
+++ b/public/examples/golomt-bank-statement-sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Голомт банк</t>
   </si>
@@ -19,9 +19,6 @@
     <t>Гүйлгээний огноо</t>
   </si>
   <si>
-    <t>Утгын огноо</t>
-  </si>
-  <si>
     <t>Гүйлгээний утга</t>
   </si>
   <si>
@@ -35,9 +32,6 @@
   </si>
   <si>
     <t>Зарлага</t>
-  </si>
-  <si>
-    <t>Үлдэгдэл</t>
   </si>
   <si>
     <t>Борлуулалтын орлого</t>
@@ -89,11 +83,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0;[Red](#,##0);-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -110,11 +103,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -136,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -144,54 +132,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color rgb="FFD7E1E5"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,189 +483,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="18" style="2" customWidth="1"/>
-    <col min="6" max="7" width="16" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1250000</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>46174</v>
-      </c>
-      <c r="B3" s="10">
-        <v>46174</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="11" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="13">
-        <v>1250000</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4">
         <v>0</v>
       </c>
-      <c r="H3" s="13">
-        <v>9500000</v>
+      <c r="F4" s="4">
+        <v>450000</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
-        <v>46175</v>
-      </c>
-      <c r="B4" s="10">
-        <v>46175</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="11" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="13">
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4">
+        <v>780000</v>
+      </c>
+      <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="13">
-        <v>450000</v>
-      </c>
-      <c r="H4" s="13">
-        <v>9050000</v>
-      </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>46176</v>
-      </c>
-      <c r="B5" s="10">
-        <v>46176</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="11" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="13">
-        <v>780000</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4">
         <v>0</v>
       </c>
-      <c r="H5" s="13">
-        <v>9830000</v>
+      <c r="F6" s="4">
+        <v>120000</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>46177</v>
-      </c>
-      <c r="B6" s="10">
-        <v>46177</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="11" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="13">
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4">
         <v>0</v>
       </c>
-      <c r="G6" s="13">
-        <v>120000</v>
-      </c>
-      <c r="H6" s="13">
-        <v>9710000</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>46178</v>
-      </c>
-      <c r="B7" s="10">
-        <v>46178</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="4">
         <v>235000</v>
-      </c>
-      <c r="H7" s="13">
-        <v>9475000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H7"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
